--- a/Cardiovascular_LRP1_Expression_Supplementary/Supplementary Table 1 and 2.xlsx
+++ b/Cardiovascular_LRP1_Expression_Supplementary/Supplementary Table 1 and 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c75c687d925685b4/7.Career/7.13 Cambridge Era/1. Science Management/3. Cam Papers/3. LRP1 Vascular  Expression/5. Resubmission/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c75c687d925685b4/7.Career/7.13 Cambridge Era/1. Science Management/3. Cam Papers/3. LRP1 Vascular  Expression/6. Resubmission_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C21A74BC-4551-0F4A-8BC7-90DADBBA1EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B939C96-2F98-C641-B722-66A692C01907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1740" windowWidth="27240" windowHeight="16440" xr2:uid="{CC49D25D-B9DA-694F-B78F-DD09FE9D9BE3}"/>
+    <workbookView xWindow="17600" yWindow="-21080" windowWidth="34480" windowHeight="19740" activeTab="1" xr2:uid="{CC49D25D-B9DA-694F-B78F-DD09FE9D9BE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplementary Table 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="382">
   <si>
     <t>Total LRP1 in Bulk Tissues (GTEx) - Number of Samples:</t>
   </si>
@@ -775,9 +775,6 @@
   </si>
   <si>
     <t>Cells Quantified</t>
-  </si>
-  <si>
-    <t>Comparison</t>
   </si>
   <si>
     <t>Aorta - Male:Female</t>
@@ -827,9 +824,6 @@
     <t>Left Ventricle - Male:Female</t>
   </si>
   <si>
-    <t>Supplementary Table 2. Statistical Analyses of Sex Differences</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -1005,17 +999,248 @@
   </si>
   <si>
     <t>Donor Details and Samples Contributed to scRNASeq (Litviňuková et al., 2020 Dataset from Supplementary Table 1 &amp; 22)</t>
+  </si>
+  <si>
+    <t>Endothelial1</t>
+  </si>
+  <si>
+    <t>Fibroblast</t>
+  </si>
+  <si>
+    <t>Macrophage</t>
+  </si>
+  <si>
+    <t>Uncharacterized</t>
+  </si>
+  <si>
+    <t>Lymphocyte</t>
+  </si>
+  <si>
+    <t>Microvasculature</t>
+  </si>
+  <si>
+    <t>Endothelial2</t>
+  </si>
+  <si>
+    <t>Smooth Muscle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplementary Table 2. </t>
+  </si>
+  <si>
+    <t>Statistical Analyses of Sex Differences</t>
+  </si>
+  <si>
+    <t>Statistical Analyses of LRP1 Pseudobulk in Arterial Cells</t>
+  </si>
+  <si>
+    <t>log2 Fold Change</t>
+  </si>
+  <si>
+    <t>Statistical Analyses of LRP1 Pseudobulk in Heart Cells</t>
+  </si>
+  <si>
+    <t>Dunn's multiple comparisons test</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Adjusted P Value</t>
+  </si>
+  <si>
+    <t>****</t>
+  </si>
+  <si>
+    <t>&lt;0.0001</t>
+  </si>
+  <si>
+    <t>Statistical Analyses of Age Differences (by Sex)</t>
+  </si>
+  <si>
+    <t>  20-29 vs. 30-39</t>
+  </si>
+  <si>
+    <t>  20-29 vs. 40-49</t>
+  </si>
+  <si>
+    <t>  20-29 vs. 50-59</t>
+  </si>
+  <si>
+    <t>  20-29 vs. 60-69</t>
+  </si>
+  <si>
+    <t>  20-29 vs. 70-79</t>
+  </si>
+  <si>
+    <t>  30-39 vs. 40-49</t>
+  </si>
+  <si>
+    <t>  30-39 vs. 50-59</t>
+  </si>
+  <si>
+    <t>  30-39 vs. 60-69</t>
+  </si>
+  <si>
+    <t>  30-39 vs. 70-79</t>
+  </si>
+  <si>
+    <t>  40-49 vs. 50-59</t>
+  </si>
+  <si>
+    <t>  40-49 vs. 60-69</t>
+  </si>
+  <si>
+    <t>  40-49 vs. 70-79</t>
+  </si>
+  <si>
+    <t>  50-59 vs. 60-69</t>
+  </si>
+  <si>
+    <t>  50-59 vs. 70-79</t>
+  </si>
+  <si>
+    <t>  60-69 vs. 70-79</t>
+  </si>
+  <si>
+    <t>&gt;0.9999</t>
+  </si>
+  <si>
+    <t>Male Aortic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female Aortic </t>
+  </si>
+  <si>
+    <t>Comparisons</t>
+  </si>
+  <si>
+    <t>Male Coronary</t>
+  </si>
+  <si>
+    <t>Female Coronary</t>
+  </si>
+  <si>
+    <t>Male Tibial</t>
+  </si>
+  <si>
+    <t>Female Tibial</t>
+  </si>
+  <si>
+    <t>Statistical Analyses of Arterial Bed/Heart Tissue Differences</t>
+  </si>
+  <si>
+    <t>Artial vs. Left Ventrical</t>
+  </si>
+  <si>
+    <t>Coronary vs. Tibial</t>
+  </si>
+  <si>
+    <t>Aorta vs. Tibial</t>
+  </si>
+  <si>
+    <t>Aorta vs. Coronary</t>
+  </si>
+  <si>
+    <t>Mann Whitney test</t>
+  </si>
+  <si>
+    <t>Male Atrial</t>
+  </si>
+  <si>
+    <t>Female Atrial</t>
+  </si>
+  <si>
+    <t>Male Left Ventricle</t>
+  </si>
+  <si>
+    <t>Female Left Ventricle</t>
+  </si>
+  <si>
+    <t>Adipocyte</t>
+  </si>
+  <si>
+    <t>Endothelial cell</t>
+  </si>
+  <si>
+    <t>Atrial Cardiomyocyte</t>
+  </si>
+  <si>
+    <t>Myeloid</t>
+  </si>
+  <si>
+    <t>Lymphoid</t>
+  </si>
+  <si>
+    <t>Neural cell</t>
+  </si>
+  <si>
+    <t>Ventricular Cardiomyocyte</t>
+  </si>
+  <si>
+    <t>Mural cell</t>
+  </si>
+  <si>
+    <t>Lymphatic Endothelial cell</t>
+  </si>
+  <si>
+    <t>Mesothelial cell</t>
+  </si>
+  <si>
+    <t>Mast cell</t>
+  </si>
+  <si>
+    <t>Cell Type A</t>
+  </si>
+  <si>
+    <t>Cell Type B</t>
+  </si>
+  <si>
+    <t>log2 fold-change standard error</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">p </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>value</t>
+    </r>
+  </si>
+  <si>
+    <t>padj gene</t>
+  </si>
+  <si>
+    <t>padj pairwise</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0E+00"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1128,6 +1353,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1178,7 +1409,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1201,25 +1432,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1228,18 +1455,47 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1606,8 +1862,8 @@
     <col min="11" max="11" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="32" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:8" s="28" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1628,7 +1884,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -1714,7 +1970,7 @@
     </row>
     <row r="10" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1916,7 +2172,7 @@
     </row>
     <row r="23" spans="1:12" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -2609,9 +2865,9 @@
         <v>315</v>
       </c>
     </row>
-    <row r="46" spans="1:16" s="30" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A46" s="29" t="s">
-        <v>260</v>
+    <row r="46" spans="1:16" s="26" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A46" s="25" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="18" x14ac:dyDescent="0.25">
@@ -3071,808 +3327,779 @@
       <c r="A66" s="2"/>
       <c r="B66" s="10"/>
     </row>
-    <row r="67" spans="1:17" s="28" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A67" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B67" s="27"/>
+    <row r="67" spans="1:17" s="24" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A67" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B67" s="23"/>
     </row>
     <row r="68" spans="1:17" ht="22" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="10"/>
     </row>
     <row r="69" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A69" s="33" t="s">
+      <c r="A69" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D69" s="34" t="s">
+      <c r="D69" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="F69" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="E69" s="34" t="s">
+      <c r="G69" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="F69" s="34" t="s">
+      <c r="H69" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="G69" s="34" t="s">
+      <c r="I69" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="H69" s="34" t="s">
+      <c r="J69" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="I69" s="34" t="s">
+      <c r="K69" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="J69" s="34" t="s">
+      <c r="L69" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="K69" s="34" t="s">
+      <c r="M69" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="L69" s="34" t="s">
+      <c r="N69" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="M69" s="34" t="s">
+      <c r="O69" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="N69" s="34" t="s">
+      <c r="P69" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="O69" s="34" t="s">
+      <c r="Q69" s="32"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="P69" s="35" t="s">
+      <c r="B70" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="Q69" s="36"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A70" s="20" t="s">
+      <c r="E70" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="F70" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="J70" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K70" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="L70" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M70" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N70" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O70" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P70" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J71" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O71" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P71" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I72" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J72" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P72" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="B73" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C73" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I73" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J73" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K73" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="L73" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="M73" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N73" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O73" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P73" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="H74" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="J74" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="K74" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L74" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M74" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N74" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O74" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P74" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K75" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M75" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N75" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O75" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P75" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="J76" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K76" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L76" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M76" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N76" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O76" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P76" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="I77" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J77" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K77" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="L77" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="M77" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N77" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O77" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P77" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D70" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E70" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F70" s="21" t="s">
+      <c r="D78" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="F78" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G70" s="21" t="s">
+      <c r="G78" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I78" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="J78" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="H70" s="21" t="s">
+      <c r="K78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O78" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P78" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I70" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="J70" s="21" t="s">
+      <c r="D79" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K79" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="K70" s="21" t="s">
+      <c r="L79" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M79" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N79" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O79" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P79" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A80" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="I80" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="J80" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L80" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M80" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N80" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O80" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P80" s="19">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J81" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M81" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N81" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="O81" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P81" s="18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M82" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N82" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O82" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P82" s="18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="M83" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="N83" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O83" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="P83" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="L70" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M70" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N70" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O70" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P70" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q70" s="19"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="F71" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="I71" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J71" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P71" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q71" s="19"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E72" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F72" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G72" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="H72" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I72" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J72" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K72" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L72" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M72" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N72" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O72" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P72" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q72" s="19"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A73" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F73" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G73" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="H73" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I73" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J73" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K73" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="L73" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="M73" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N73" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O73" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P73" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q73" s="19"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F74" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G74" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="H74" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="I74" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="J74" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="K74" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L74" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M74" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N74" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O74" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P74" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q74" s="19"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A75" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E75" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G75" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="H75" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I75" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="J75" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K75" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L75" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M75" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N75" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O75" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P75" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q75" s="19"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A76" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="H76" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I76" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="J76" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K76" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L76" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M76" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N76" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O76" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P76" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q76" s="19"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E77" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="H77" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="I77" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J77" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K77" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="L77" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="M77" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N77" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O77" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P77" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q77" s="19"/>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E78" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I78" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="J78" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K78" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L78" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M78" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N78" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O78" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P78" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q78" s="19"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="B79" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="E79" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H79" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I79" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J79" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K79" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L79" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M79" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N79" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O79" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P79" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q79" s="19"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A80" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E80" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G80" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="J80" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K80" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L80" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M80" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N80" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O80" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P80" s="22">
-        <v>0.6</v>
-      </c>
-      <c r="Q80" s="19"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A81" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E81" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="F81" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G81" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H81" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I81" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="J81" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K81" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L81" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M81" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N81" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="O81" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P81" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q81" s="19"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E82" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="F82" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I82" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="J82" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K82" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L82" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M82" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N82" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O82" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P82" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q82" s="19"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B83" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E83" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F83" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="H83" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="I83" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="J83" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="K83" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="L83" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="M83" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="N83" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O83" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="P83" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q83" s="19"/>
-    </row>
-    <row r="84" spans="1:17" ht="22" x14ac:dyDescent="0.3">
-      <c r="A84" s="24"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
-      <c r="O84" s="19"/>
-      <c r="P84" s="19"/>
-      <c r="Q84" s="19"/>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:16" ht="22" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="21"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>60</v>
@@ -3902,7 +4129,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>1</v>
       </c>
@@ -3937,7 +4164,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>2</v>
       </c>
@@ -3972,7 +4199,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>3</v>
       </c>
@@ -4004,7 +4231,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4</v>
       </c>
@@ -4036,9 +4263,9 @@
         <v>72</v>
       </c>
       <c r="K90" s="16"/>
-      <c r="L90" s="17"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>5</v>
       </c>
@@ -4069,10 +4296,8 @@
       <c r="J91" t="s">
         <v>72</v>
       </c>
-      <c r="K91" s="18"/>
-      <c r="L91" s="18"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>6</v>
       </c>
@@ -4103,10 +4328,8 @@
       <c r="J92" t="s">
         <v>72</v>
       </c>
-      <c r="K92" s="18"/>
-      <c r="L92" s="18"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>7</v>
       </c>
@@ -4137,10 +4360,10 @@
       <c r="J93" t="s">
         <v>72</v>
       </c>
-      <c r="K93" s="17"/>
-      <c r="L93" s="17"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>8</v>
       </c>
@@ -4171,10 +4394,8 @@
       <c r="J94" t="s">
         <v>72</v>
       </c>
-      <c r="K94" s="18"/>
-      <c r="L94" s="18"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>9</v>
       </c>
@@ -4205,10 +4426,8 @@
       <c r="J95" t="s">
         <v>72</v>
       </c>
-      <c r="K95" s="18"/>
-      <c r="L95" s="18"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>10</v>
       </c>
@@ -4239,8 +4458,6 @@
       <c r="J96" t="s">
         <v>72</v>
       </c>
-      <c r="K96" s="18"/>
-      <c r="L96" s="18"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97">
@@ -8734,105 +8951,3026 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4071C1C9-172A-C141-8C31-9826F5322A4A}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B13">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="C13">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D13">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="C14">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="D14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>248</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B15">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="C15">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="D15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3">
-        <v>1.9199999999999998E-2</v>
-      </c>
-      <c r="C3">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="D3">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B4">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="C4">
-        <v>0.41399999999999998</v>
-      </c>
-      <c r="D4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5">
-        <v>0.60199999999999998</v>
-      </c>
-      <c r="C5">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="D5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B16" s="12">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="C16" s="12">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="12">
-        <v>0.44700000000000001</v>
-      </c>
-      <c r="C6" s="12">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D6" s="12">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7">
+      <c r="B17">
         <v>0.14699999999999999</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C17" s="12">
         <v>0.20899999999999999</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D17" s="12">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>328</v>
+      </c>
+      <c r="K22" s="49" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C23" t="s">
+        <v>347</v>
+      </c>
+      <c r="D23" t="s">
+        <v>347</v>
+      </c>
+      <c r="E23" t="s">
+        <v>347</v>
+      </c>
+      <c r="F23" s="47">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J23" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K23" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" t="s">
+        <v>347</v>
+      </c>
+      <c r="C24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D24" t="s">
+        <v>347</v>
+      </c>
+      <c r="E24" t="s">
+        <v>347</v>
+      </c>
+      <c r="F24" s="47">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="G24" s="47">
+        <v>2.92E-2</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" t="s">
+        <v>347</v>
+      </c>
+      <c r="C25" t="s">
+        <v>347</v>
+      </c>
+      <c r="D25" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" t="s">
+        <v>347</v>
+      </c>
+      <c r="F25" s="47">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="G25" s="47">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J25" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K25" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" t="s">
+        <v>347</v>
+      </c>
+      <c r="D26" t="s">
+        <v>347</v>
+      </c>
+      <c r="E26" t="s">
+        <v>347</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>330</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>330</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K26" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" t="s">
+        <v>347</v>
+      </c>
+      <c r="C27" t="s">
+        <v>347</v>
+      </c>
+      <c r="D27" t="s">
+        <v>347</v>
+      </c>
+      <c r="E27" t="s">
+        <v>347</v>
+      </c>
+      <c r="F27" s="47">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="G27" s="47">
+        <v>1.9E-3</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J27" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K27" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>337</v>
+      </c>
+      <c r="B28" t="s">
+        <v>347</v>
+      </c>
+      <c r="C28" t="s">
+        <v>347</v>
+      </c>
+      <c r="D28" t="s">
+        <v>347</v>
+      </c>
+      <c r="E28" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="47">
+        <v>0.6704</v>
+      </c>
+      <c r="G28" s="47">
+        <v>0.81330000000000002</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J28" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K28" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" t="s">
+        <v>347</v>
+      </c>
+      <c r="D29" t="s">
+        <v>347</v>
+      </c>
+      <c r="E29" t="s">
+        <v>347</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="G29" s="47">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J29" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K29" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>339</v>
+      </c>
+      <c r="B30" t="s">
+        <v>347</v>
+      </c>
+      <c r="C30" t="s">
+        <v>347</v>
+      </c>
+      <c r="D30" t="s">
+        <v>347</v>
+      </c>
+      <c r="E30" t="s">
+        <v>347</v>
+      </c>
+      <c r="F30" s="47">
+        <v>9.9299999999999999E-2</v>
+      </c>
+      <c r="G30" s="47">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I30" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J30" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K30" s="47">
+        <v>0.66549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>340</v>
+      </c>
+      <c r="B31" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" t="s">
+        <v>347</v>
+      </c>
+      <c r="D31" t="s">
+        <v>347</v>
+      </c>
+      <c r="E31" t="s">
+        <v>347</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="G31" s="47">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I31" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J31" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K31" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>341</v>
+      </c>
+      <c r="B32" t="s">
+        <v>347</v>
+      </c>
+      <c r="C32" t="s">
+        <v>347</v>
+      </c>
+      <c r="D32" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" t="s">
+        <v>347</v>
+      </c>
+      <c r="F32" t="s">
+        <v>347</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I32" t="s">
+        <v>347</v>
+      </c>
+      <c r="J32" t="s">
+        <v>347</v>
+      </c>
+      <c r="K32" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" t="s">
+        <v>347</v>
+      </c>
+      <c r="C33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D33" s="47">
+        <v>0.1061</v>
+      </c>
+      <c r="E33" t="s">
+        <v>347</v>
+      </c>
+      <c r="F33" t="s">
+        <v>347</v>
+      </c>
+      <c r="G33" s="47">
+        <v>0.379</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I33" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J33" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K33" s="47">
+        <v>0.60499999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>343</v>
+      </c>
+      <c r="B34" t="s">
+        <v>347</v>
+      </c>
+      <c r="C34" t="s">
+        <v>347</v>
+      </c>
+      <c r="D34" s="47">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>347</v>
+      </c>
+      <c r="F34" t="s">
+        <v>347</v>
+      </c>
+      <c r="G34" s="47">
+        <v>0.46560000000000001</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I34" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J34" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K34" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" t="s">
+        <v>347</v>
+      </c>
+      <c r="D35" s="47">
+        <v>0.74929999999999997</v>
+      </c>
+      <c r="E35" t="s">
+        <v>347</v>
+      </c>
+      <c r="F35" t="s">
+        <v>347</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H35" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I35" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J35" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K35" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>345</v>
+      </c>
+      <c r="B36" t="s">
+        <v>347</v>
+      </c>
+      <c r="C36" t="s">
+        <v>347</v>
+      </c>
+      <c r="D36" s="47">
+        <v>0.31790000000000002</v>
+      </c>
+      <c r="E36" t="s">
+        <v>347</v>
+      </c>
+      <c r="F36" t="s">
+        <v>347</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H36" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I36" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J36" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K36" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>346</v>
+      </c>
+      <c r="B37" t="s">
+        <v>347</v>
+      </c>
+      <c r="C37" t="s">
+        <v>347</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="E37" t="s">
+        <v>347</v>
+      </c>
+      <c r="F37" t="s">
+        <v>347</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I37" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="J37" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K37" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>313</v>
+      </c>
+      <c r="B42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C42" s="45">
+        <v>-5.1018011473020604</v>
+      </c>
+      <c r="D42" s="41">
+        <v>0.19886026547729099</v>
+      </c>
+      <c r="E42" s="39">
+        <v>3.6986961550934203E-145</v>
+      </c>
+      <c r="F42" s="34">
+        <v>1.4802798462043001E-141</v>
+      </c>
+      <c r="G42" s="35">
+        <v>1.0356349234261501E-143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="45">
+        <v>-4.3893681223061201</v>
+      </c>
+      <c r="D43" s="41">
+        <v>0.19888985031551801</v>
+      </c>
+      <c r="E43" s="39">
+        <v>6.2291440074217902E-108</v>
+      </c>
+      <c r="F43" s="34">
+        <v>1.41349659435079E-105</v>
+      </c>
+      <c r="G43" s="35">
+        <v>8.7208016103905095E-107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>313</v>
+      </c>
+      <c r="B44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44" s="45">
+        <v>-3.9685929307769299</v>
+      </c>
+      <c r="D44" s="41">
+        <v>0.20526479219135399</v>
+      </c>
+      <c r="E44" s="39">
+        <v>2.7791520942927399E-83</v>
+      </c>
+      <c r="F44" s="34">
+        <v>4.2567925234270101E-80</v>
+      </c>
+      <c r="G44" s="35">
+        <v>1.5563251728039299E-82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>313</v>
+      </c>
+      <c r="B45" t="s">
+        <v>317</v>
+      </c>
+      <c r="C45" s="45">
+        <v>-2.0526281188166902</v>
+      </c>
+      <c r="D45" s="41">
+        <v>0.204833176746684</v>
+      </c>
+      <c r="E45" s="39">
+        <v>1.23280859253826E-23</v>
+      </c>
+      <c r="F45" s="34">
+        <v>2.7020682646146199E-22</v>
+      </c>
+      <c r="G45" s="35">
+        <v>2.30124270607142E-23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>313</v>
+      </c>
+      <c r="B46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="45">
+        <v>-1.7155369464774799</v>
+      </c>
+      <c r="D46" s="41">
+        <v>0.199678818441135</v>
+      </c>
+      <c r="E46" s="39">
+        <v>8.5854764997436504E-18</v>
+      </c>
+      <c r="F46" s="34">
+        <v>8.72949573372119E-17</v>
+      </c>
+      <c r="G46" s="35">
+        <v>1.33551856662679E-17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>313</v>
+      </c>
+      <c r="B47" t="s">
+        <v>319</v>
+      </c>
+      <c r="C47" s="45">
+        <v>-0.92861256885535404</v>
+      </c>
+      <c r="D47" s="41">
+        <v>0.215470022189412</v>
+      </c>
+      <c r="E47" s="39">
+        <v>1.63471306516006E-5</v>
+      </c>
+      <c r="F47" s="34">
+        <v>1.4615113237323899E-4</v>
+      </c>
+      <c r="G47" s="35">
+        <v>2.0805439011127999E-5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>319</v>
+      </c>
+      <c r="B48" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" s="45">
+        <v>-4.1731885784467098</v>
+      </c>
+      <c r="D48" s="41">
+        <v>0.21357534268922701</v>
+      </c>
+      <c r="E48" s="39">
+        <v>5.0522238594726702E-85</v>
+      </c>
+      <c r="F48" s="34">
+        <v>3.27889328479776E-82</v>
+      </c>
+      <c r="G48" s="35">
+        <v>3.5365567016308698E-84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>319</v>
+      </c>
+      <c r="B49" t="s">
+        <v>315</v>
+      </c>
+      <c r="C49" s="45">
+        <v>-3.4607555534507699</v>
+      </c>
+      <c r="D49" s="41">
+        <v>0.21360325919701301</v>
+      </c>
+      <c r="E49" s="39">
+        <v>4.8978829470479103E-59</v>
+      </c>
+      <c r="F49" s="34">
+        <v>2.9710994401807698E-57</v>
+      </c>
+      <c r="G49" s="35">
+        <v>1.9591531788191599E-58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>319</v>
+      </c>
+      <c r="B50" t="s">
+        <v>316</v>
+      </c>
+      <c r="C50" s="45">
+        <v>-3.03998036192157</v>
+      </c>
+      <c r="D50" s="41">
+        <v>0.219374138058854</v>
+      </c>
+      <c r="E50" s="39">
+        <v>1.14572836704311E-43</v>
+      </c>
+      <c r="F50" s="34">
+        <v>3.0984414641890799E-41</v>
+      </c>
+      <c r="G50" s="35">
+        <v>3.2080394277207E-43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>319</v>
+      </c>
+      <c r="B51" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" s="45">
+        <v>-1.12401554996134</v>
+      </c>
+      <c r="D51" s="41">
+        <v>0.219139942821199</v>
+      </c>
+      <c r="E51" s="39">
+        <v>2.9095523471792901E-7</v>
+      </c>
+      <c r="F51" s="34">
+        <v>1.4321423553306099E-6</v>
+      </c>
+      <c r="G51" s="35">
+        <v>3.8794031295723901E-7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>319</v>
+      </c>
+      <c r="B52" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" s="45">
+        <v>-0.78692437762212597</v>
+      </c>
+      <c r="D52" s="41">
+        <v>0.214323725340273</v>
+      </c>
+      <c r="E52" s="39">
+        <v>2.4097781299089601E-4</v>
+      </c>
+      <c r="F52" s="34">
+        <v>8.3260434868350798E-4</v>
+      </c>
+      <c r="G52" s="35">
+        <v>2.9336429407587298E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>314</v>
+      </c>
+      <c r="B53" t="s">
+        <v>318</v>
+      </c>
+      <c r="C53" s="46">
+        <v>3.3862642008245798</v>
+      </c>
+      <c r="D53" s="41">
+        <v>0.19758271235073499</v>
+      </c>
+      <c r="E53" s="39">
+        <v>7.6648848457887497E-66</v>
+      </c>
+      <c r="F53" s="34">
+        <v>3.4891329519461801E-63</v>
+      </c>
+      <c r="G53" s="35">
+        <v>3.5769462613680798E-65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>314</v>
+      </c>
+      <c r="B54" t="s">
+        <v>317</v>
+      </c>
+      <c r="C54" s="46">
+        <v>3.04917302848536</v>
+      </c>
+      <c r="D54" s="42">
+        <v>0.202787688758648</v>
+      </c>
+      <c r="E54" s="39">
+        <v>4.24740193539843E-51</v>
+      </c>
+      <c r="F54" s="34">
+        <v>5.5962945823015701E-49</v>
+      </c>
+      <c r="G54" s="35">
+        <v>1.4865906773894499E-50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>314</v>
+      </c>
+      <c r="B55" t="s">
+        <v>316</v>
+      </c>
+      <c r="C55" s="46">
+        <v>1.13320821652513</v>
+      </c>
+      <c r="D55" s="41">
+        <v>0.20326117685050299</v>
+      </c>
+      <c r="E55" s="39">
+        <v>2.47339971853881E-8</v>
+      </c>
+      <c r="F55" s="34">
+        <v>6.8959734814824596E-7</v>
+      </c>
+      <c r="G55" s="35">
+        <v>3.6450101115308899E-8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>314</v>
+      </c>
+      <c r="B56" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" s="46">
+        <v>0.71243302499593697</v>
+      </c>
+      <c r="D56" s="41">
+        <v>0.19678245599710401</v>
+      </c>
+      <c r="E56" s="39">
+        <v>2.9413739914716902E-4</v>
+      </c>
+      <c r="F56" s="34">
+        <v>5.9352409722377797E-4</v>
+      </c>
+      <c r="G56" s="35">
+        <v>3.4316029900503098E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" t="s">
+        <v>315</v>
+      </c>
+      <c r="C57" s="45">
+        <v>-2.3367400034894201</v>
+      </c>
+      <c r="D57" s="41">
+        <v>0.20281616540507699</v>
+      </c>
+      <c r="E57" s="39">
+        <v>1.02843475886626E-30</v>
+      </c>
+      <c r="F57" s="34">
+        <v>5.3454120919168197E-29</v>
+      </c>
+      <c r="G57" s="35">
+        <v>2.21509024986581E-30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>317</v>
+      </c>
+      <c r="B58" t="s">
+        <v>316</v>
+      </c>
+      <c r="C58" s="45">
+        <v>-1.9159648119602299</v>
+      </c>
+      <c r="D58" s="41">
+        <v>0.209115184341153</v>
+      </c>
+      <c r="E58" s="39">
+        <v>5.0828098746262197E-20</v>
+      </c>
+      <c r="F58" s="34">
+        <v>2.72759768546195E-18</v>
+      </c>
+      <c r="G58" s="35">
+        <v>8.3716868523255396E-20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>317</v>
+      </c>
+      <c r="B59" t="s">
+        <v>318</v>
+      </c>
+      <c r="C59" s="46">
+        <v>0.33709117233921698</v>
+      </c>
+      <c r="D59" s="41">
+        <v>0.20359077847461801</v>
+      </c>
+      <c r="E59" s="40">
+        <v>9.7776695505158398E-2</v>
+      </c>
+      <c r="F59" s="36">
+        <v>0.15850641255752901</v>
+      </c>
+      <c r="G59" s="35">
+        <v>0.101398054597942</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="46">
+        <v>2.6738311758286399</v>
+      </c>
+      <c r="D60" s="41">
+        <v>0.197612354892125</v>
+      </c>
+      <c r="E60" s="39">
+        <v>1.03054204784876E-41</v>
+      </c>
+      <c r="F60" s="34">
+        <v>1.4265031124960101E-40</v>
+      </c>
+      <c r="G60" s="35">
+        <v>2.6231979399786799E-41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>316</v>
+      </c>
+      <c r="C61" s="46">
+        <v>0.42077519152919401</v>
+      </c>
+      <c r="D61" s="41">
+        <v>0.20329086571271801</v>
+      </c>
+      <c r="E61" s="39">
+        <v>3.8469345741273302E-2</v>
+      </c>
+      <c r="F61" s="37">
+        <v>7.2358129031317095E-2</v>
+      </c>
+      <c r="G61" s="33">
+        <v>4.3085667230226103E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>318</v>
+      </c>
+      <c r="B62" t="s">
+        <v>316</v>
+      </c>
+      <c r="C62" s="45">
+        <v>-2.2530559842994502</v>
+      </c>
+      <c r="D62" s="41">
+        <v>0.204052345042679</v>
+      </c>
+      <c r="E62" s="39">
+        <v>2.4081842935313498E-28</v>
+      </c>
+      <c r="F62" s="34">
+        <v>2.51137755240735E-26</v>
+      </c>
+      <c r="G62" s="35">
+        <v>4.8163685870626996E-28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" t="s">
+        <v>313</v>
+      </c>
+      <c r="C63" s="46">
+        <v>4.0145570571154696</v>
+      </c>
+      <c r="D63" s="41">
+        <v>0.198880800513864</v>
+      </c>
+      <c r="E63" s="39">
+        <v>1.3064418424247E-90</v>
+      </c>
+      <c r="F63" s="34">
+        <v>3.2341843259942798E-88</v>
+      </c>
+      <c r="G63" s="35">
+        <v>1.2193457195963901E-89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="46">
+        <v>3.0859444882601101</v>
+      </c>
+      <c r="D64" s="41">
+        <v>0.21359345205715599</v>
+      </c>
+      <c r="E64" s="39">
+        <v>2.5901495951226298E-47</v>
+      </c>
+      <c r="F64" s="34">
+        <v>2.3774080946693001E-45</v>
+      </c>
+      <c r="G64" s="35">
+        <v>8.0582431848259602E-47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" t="s">
+        <v>318</v>
+      </c>
+      <c r="C65" s="46">
+        <v>2.2990201106379802</v>
+      </c>
+      <c r="D65" s="41">
+        <v>0.197603460808285</v>
+      </c>
+      <c r="E65" s="39">
+        <v>2.7515482717574398E-31</v>
+      </c>
+      <c r="F65" s="34">
+        <v>3.1566298661068999E-29</v>
+      </c>
+      <c r="G65" s="35">
+        <v>6.4202793007673596E-31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="46">
+        <v>1.9619289382987699</v>
+      </c>
+      <c r="D66" s="41">
+        <v>0.202807919355799</v>
+      </c>
+      <c r="E66" s="39">
+        <v>3.8952887579101599E-22</v>
+      </c>
+      <c r="F66" s="34">
+        <v>6.0904386639469597E-21</v>
+      </c>
+      <c r="G66" s="35">
+        <v>6.8167553263427801E-22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" s="45">
+        <v>-1.0872440901865901</v>
+      </c>
+      <c r="D67" s="41">
+        <v>0.196773594360038</v>
+      </c>
+      <c r="E67" s="39">
+        <v>3.2881884486250803E-8</v>
+      </c>
+      <c r="F67" s="34">
+        <v>3.8544685612655099E-7</v>
+      </c>
+      <c r="G67" s="35">
+        <v>4.60346382807512E-8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" t="s">
+        <v>315</v>
+      </c>
+      <c r="C68" s="45">
+        <v>-0.37481106519065599</v>
+      </c>
+      <c r="D68" s="41">
+        <v>0.196803338157201</v>
+      </c>
+      <c r="E68" s="39">
+        <v>5.6845686618827503E-2</v>
+      </c>
+      <c r="F68" s="37">
+        <v>8.1984112479153395E-2</v>
+      </c>
+      <c r="G68" s="33">
+        <v>6.1218431743352703E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" s="45">
+        <v>4.5964126338538802E-2</v>
+      </c>
+      <c r="D69" s="41">
+        <v>0.20328073862206</v>
+      </c>
+      <c r="E69" s="40">
+        <v>0.82111464843052495</v>
+      </c>
+      <c r="F69" s="38">
+        <v>0.88738297204071903</v>
+      </c>
+      <c r="G69" s="33">
+        <v>0.82111464843052495</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D70" s="42"/>
+    </row>
+    <row r="71" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G72" s="43" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>365</v>
+      </c>
+      <c r="B73" t="s">
+        <v>366</v>
+      </c>
+      <c r="C73" s="42">
+        <v>5.3736021944536896</v>
+      </c>
+      <c r="D73" s="42">
+        <v>0.23283564621564601</v>
+      </c>
+      <c r="E73" s="33">
+        <v>7.5345390379537598E-118</v>
+      </c>
+      <c r="F73" s="33">
+        <v>6.6332198055385401E-115</v>
+      </c>
+      <c r="G73" s="33">
+        <v>4.9727957650494799E-116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>366</v>
+      </c>
+      <c r="B74" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="42">
+        <v>-5.3217031052647901</v>
+      </c>
+      <c r="D74" s="42">
+        <v>0.23199667645623301</v>
+      </c>
+      <c r="E74" s="33">
+        <v>1.9103571221740899E-116</v>
+      </c>
+      <c r="F74" s="33">
+        <v>2.8642621118463601E-113</v>
+      </c>
+      <c r="G74" s="33">
+        <v>6.3041785031745199E-115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>365</v>
+      </c>
+      <c r="B75" t="s">
+        <v>367</v>
+      </c>
+      <c r="C75" s="42">
+        <v>5.1797684916890301</v>
+      </c>
+      <c r="D75" s="42">
+        <v>0.23065771150161199</v>
+      </c>
+      <c r="E75" s="33">
+        <v>1.10523056822268E-111</v>
+      </c>
+      <c r="F75" s="33">
+        <v>7.4134656114212998E-109</v>
+      </c>
+      <c r="G75" s="33">
+        <v>2.4315072500899001E-110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>367</v>
+      </c>
+      <c r="B76" t="s">
+        <v>314</v>
+      </c>
+      <c r="C76" s="42">
+        <v>-5.1278694025001199</v>
+      </c>
+      <c r="D76" s="42">
+        <v>0.22981649600815501</v>
+      </c>
+      <c r="E76" s="33">
+        <v>2.7702922801708899E-110</v>
+      </c>
+      <c r="F76" s="33">
+        <v>2.7283362865557503E-107</v>
+      </c>
+      <c r="G76" s="33">
+        <v>4.5709822622819702E-109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>366</v>
+      </c>
+      <c r="B77" t="s">
+        <v>368</v>
+      </c>
+      <c r="C77" s="42">
+        <v>-4.9911533587912897</v>
+      </c>
+      <c r="D77" s="42">
+        <v>0.23221172924818101</v>
+      </c>
+      <c r="E77" s="33">
+        <v>1.77261906828771E-102</v>
+      </c>
+      <c r="F77" s="33">
+        <v>3.9747019433638399E-100</v>
+      </c>
+      <c r="G77" s="33">
+        <v>2.33985717013978E-101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>367</v>
+      </c>
+      <c r="B78" t="s">
+        <v>368</v>
+      </c>
+      <c r="C78" s="42">
+        <v>-4.7973196560266302</v>
+      </c>
+      <c r="D78" s="42">
+        <v>0.230033691125269</v>
+      </c>
+      <c r="E78" s="33">
+        <v>1.3771020533744E-96</v>
+      </c>
+      <c r="F78" s="33">
+        <v>1.3516183143084E-94</v>
+      </c>
+      <c r="G78" s="33">
+        <v>1.51481225871185E-95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>365</v>
+      </c>
+      <c r="B79" t="s">
+        <v>369</v>
+      </c>
+      <c r="C79" s="42">
+        <v>4.7419370751662697</v>
+      </c>
+      <c r="D79" s="42">
+        <v>0.246472886614333</v>
+      </c>
+      <c r="E79" s="33">
+        <v>1.73926774597322E-82</v>
+      </c>
+      <c r="F79" s="33">
+        <v>2.3664799702427501E-80</v>
+      </c>
+      <c r="G79" s="33">
+        <v>1.6398810176319001E-81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>314</v>
+      </c>
+      <c r="B80" t="s">
+        <v>369</v>
+      </c>
+      <c r="C80" s="42">
+        <v>4.6900379859773604</v>
+      </c>
+      <c r="D80" s="42">
+        <v>0.245716511180647</v>
+      </c>
+      <c r="E80" s="33">
+        <v>3.22659340795644E-81</v>
+      </c>
+      <c r="F80" s="33">
+        <v>3.9280495683528202E-79</v>
+      </c>
+      <c r="G80" s="33">
+        <v>2.6619395615640599E-80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>369</v>
+      </c>
+      <c r="B81" t="s">
+        <v>368</v>
+      </c>
+      <c r="C81" s="42">
+        <v>-4.3594882395038699</v>
+      </c>
+      <c r="D81" s="42">
+        <v>0.245904658060253</v>
+      </c>
+      <c r="E81" s="33">
+        <v>2.5328080569570098E-70</v>
+      </c>
+      <c r="F81" s="33">
+        <v>6.9275988913197098E-68</v>
+      </c>
+      <c r="G81" s="33">
+        <v>1.85739257510181E-69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>366</v>
+      </c>
+      <c r="B82" t="s">
+        <v>370</v>
+      </c>
+      <c r="C82" s="42">
+        <v>-3.61773079042944</v>
+      </c>
+      <c r="D82" s="42">
+        <v>0.23787363973727499</v>
+      </c>
+      <c r="E82" s="33">
+        <v>3.0998956189689002E-52</v>
+      </c>
+      <c r="F82" s="33">
+        <v>2.8526813727414098E-50</v>
+      </c>
+      <c r="G82" s="33">
+        <v>2.0459311085194699E-51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>365</v>
+      </c>
+      <c r="B83" t="s">
+        <v>371</v>
+      </c>
+      <c r="C83" s="42">
+        <v>3.3604647120248599</v>
+      </c>
+      <c r="D83" s="42">
+        <v>0.23040253321461199</v>
+      </c>
+      <c r="E83" s="33">
+        <v>3.48949385467129E-48</v>
+      </c>
+      <c r="F83" s="33">
+        <v>1.8726082320105399E-46</v>
+      </c>
+      <c r="G83" s="33">
+        <v>2.0936963128027699E-47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>367</v>
+      </c>
+      <c r="B84" t="s">
+        <v>370</v>
+      </c>
+      <c r="C84" s="42">
+        <v>-3.4238970876647699</v>
+      </c>
+      <c r="D84" s="42">
+        <v>0.23572513635741801</v>
+      </c>
+      <c r="E84" s="33">
+        <v>8.4197106233087205E-48</v>
+      </c>
+      <c r="F84" s="33">
+        <v>5.6690143361892398E-46</v>
+      </c>
+      <c r="G84" s="33">
+        <v>4.6308408428197997E-47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>314</v>
+      </c>
+      <c r="B85" t="s">
+        <v>371</v>
+      </c>
+      <c r="C85" s="42">
+        <v>3.3085656228359599</v>
+      </c>
+      <c r="D85" s="42">
+        <v>0.22954229137271001</v>
+      </c>
+      <c r="E85" s="33">
+        <v>4.2403575620441401E-47</v>
+      </c>
+      <c r="F85" s="33">
+        <v>1.0266805127494701E-45</v>
+      </c>
+      <c r="G85" s="33">
+        <v>2.15279691611472E-46</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" t="s">
+        <v>366</v>
+      </c>
+      <c r="C86" s="42">
+        <v>3.3443811475473102</v>
+      </c>
+      <c r="D86" s="42">
+        <v>0.23253237068726501</v>
+      </c>
+      <c r="E86" s="33">
+        <v>6.6707987240653496E-47</v>
+      </c>
+      <c r="F86" s="33">
+        <v>3.73847989639977E-45</v>
+      </c>
+      <c r="G86" s="33">
+        <v>3.1448051127736601E-46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>365</v>
+      </c>
+      <c r="B87" t="s">
+        <v>373</v>
+      </c>
+      <c r="C87" s="42">
+        <v>4.5509381657164099</v>
+      </c>
+      <c r="D87" s="42">
+        <v>0.325624976769258</v>
+      </c>
+      <c r="E87" s="33">
+        <v>2.1839102158441599E-44</v>
+      </c>
+      <c r="F87" s="33">
+        <v>3.48428632045224E-42</v>
+      </c>
+      <c r="G87" s="33">
+        <v>9.6092049497143195E-44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>314</v>
+      </c>
+      <c r="B88" t="s">
+        <v>373</v>
+      </c>
+      <c r="C88" s="42">
+        <v>4.4990390765275103</v>
+      </c>
+      <c r="D88" s="42">
+        <v>0.32506326554146198</v>
+      </c>
+      <c r="E88" s="33">
+        <v>1.4518722352592401E-43</v>
+      </c>
+      <c r="F88" s="33">
+        <v>2.2508441592412399E-41</v>
+      </c>
+      <c r="G88" s="33">
+        <v>5.9889729704443701E-43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>372</v>
+      </c>
+      <c r="B89" t="s">
+        <v>367</v>
+      </c>
+      <c r="C89" s="42">
+        <v>3.15054744478264</v>
+      </c>
+      <c r="D89" s="42">
+        <v>0.23035729938675101</v>
+      </c>
+      <c r="E89" s="33">
+        <v>1.39734093467427E-42</v>
+      </c>
+      <c r="F89" s="33">
+        <v>3.2918193812424801E-41</v>
+      </c>
+      <c r="G89" s="33">
+        <v>5.4249706875589303E-42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>368</v>
+      </c>
+      <c r="B90" t="s">
+        <v>371</v>
+      </c>
+      <c r="C90" s="42">
+        <v>2.97801587636246</v>
+      </c>
+      <c r="D90" s="42">
+        <v>0.229766379731841</v>
+      </c>
+      <c r="E90" s="33">
+        <v>2.0341650589825301E-38</v>
+      </c>
+      <c r="F90" s="33">
+        <v>2.2977745806598201E-37</v>
+      </c>
+      <c r="G90" s="33">
+        <v>7.4586052162693005E-38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>373</v>
+      </c>
+      <c r="B91" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="42">
+        <v>-4.16848933005401</v>
+      </c>
+      <c r="D91" s="42">
+        <v>0.325201076984027</v>
+      </c>
+      <c r="E91" s="33">
+        <v>1.29692060973219E-37</v>
+      </c>
+      <c r="F91" s="33">
+        <v>7.78177845615542E-36</v>
+      </c>
+      <c r="G91" s="33">
+        <v>4.5050926443328998E-37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>366</v>
+      </c>
+      <c r="B92" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" s="42">
+        <v>-3.7125367524153998</v>
+      </c>
+      <c r="D92" s="42">
+        <v>0.29109112276628901</v>
+      </c>
+      <c r="E92" s="33">
+        <v>2.9666584751175199E-37</v>
+      </c>
+      <c r="F92" s="33">
+        <v>7.6783658041156201E-35</v>
+      </c>
+      <c r="G92" s="33">
+        <v>9.7899729678878298E-37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>367</v>
+      </c>
+      <c r="B93" t="s">
+        <v>374</v>
+      </c>
+      <c r="C93" s="42">
+        <v>-3.5187030496507301</v>
+      </c>
+      <c r="D93" s="42">
+        <v>0.28929007721459499</v>
+      </c>
+      <c r="E93" s="33">
+        <v>4.8787957749170398E-34</v>
+      </c>
+      <c r="F93" s="33">
+        <v>5.0608455395217101E-32</v>
+      </c>
+      <c r="G93" s="33">
+        <v>1.53333581497392E-33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>365</v>
+      </c>
+      <c r="B94" t="s">
+        <v>375</v>
+      </c>
+      <c r="C94" s="42">
+        <v>3.9911472621848998</v>
+      </c>
+      <c r="D94" s="42">
+        <v>0.33354854772618903</v>
+      </c>
+      <c r="E94" s="33">
+        <v>5.3731947539407403E-33</v>
+      </c>
+      <c r="F94" s="33">
+        <v>3.8755652382477698E-31</v>
+      </c>
+      <c r="G94" s="33">
+        <v>1.61195842618222E-32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>369</v>
+      </c>
+      <c r="B95" t="s">
+        <v>370</v>
+      </c>
+      <c r="C95" s="42">
+        <v>-2.9860656711420099</v>
+      </c>
+      <c r="D95" s="42">
+        <v>0.25106183026626999</v>
+      </c>
+      <c r="E95" s="33">
+        <v>1.27554322178648E-32</v>
+      </c>
+      <c r="F95" s="33">
+        <v>2.9205073021276299E-31</v>
+      </c>
+      <c r="G95" s="33">
+        <v>3.66025446251773E-32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>314</v>
+      </c>
+      <c r="B96" t="s">
+        <v>375</v>
+      </c>
+      <c r="C96" s="42">
+        <v>3.9392481729959901</v>
+      </c>
+      <c r="D96" s="42">
+        <v>0.33303153851925199</v>
+      </c>
+      <c r="E96" s="33">
+        <v>2.7821941901928501E-32</v>
+      </c>
+      <c r="F96" s="33">
+        <v>1.8431885631817699E-30</v>
+      </c>
+      <c r="G96" s="33">
+        <v>7.6510340230303395E-32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>372</v>
+      </c>
+      <c r="B97" t="s">
+        <v>369</v>
+      </c>
+      <c r="C97" s="42">
+        <v>2.7127160282598801</v>
+      </c>
+      <c r="D97" s="42">
+        <v>0.24622251414906099</v>
+      </c>
+      <c r="E97" s="33">
+        <v>3.1525321714872702E-28</v>
+      </c>
+      <c r="F97" s="33">
+        <v>4.6256841841218498E-27</v>
+      </c>
+      <c r="G97" s="33">
+        <v>8.3226849327264095E-28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>375</v>
+      </c>
+      <c r="B98" t="s">
+        <v>368</v>
+      </c>
+      <c r="C98" s="42">
+        <v>-3.6086984265224999</v>
+      </c>
+      <c r="D98" s="42">
+        <v>0.33317450658306702</v>
+      </c>
+      <c r="E98" s="33">
+        <v>2.44774105928315E-27</v>
+      </c>
+      <c r="F98" s="33">
+        <v>1.7841637157891801E-25</v>
+      </c>
+      <c r="G98" s="33">
+        <v>6.2134965351033999E-27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>369</v>
+      </c>
+      <c r="B99" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="42">
+        <v>-3.0808716331279702</v>
+      </c>
+      <c r="D99" s="42">
+        <v>0.30258438550105299</v>
+      </c>
+      <c r="E99" s="33">
+        <v>2.3895148049657201E-24</v>
+      </c>
+      <c r="F99" s="33">
+        <v>7.4467439646540504E-23</v>
+      </c>
+      <c r="G99" s="33">
+        <v>5.8410361899162102E-24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>372</v>
+      </c>
+      <c r="B100" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" s="42">
+        <v>-2.0292210469063798</v>
+      </c>
+      <c r="D100" s="42">
+        <v>0.226936254055948</v>
+      </c>
+      <c r="E100" s="33">
+        <v>3.82844650800292E-19</v>
+      </c>
+      <c r="F100" s="33">
+        <v>7.53703668927033E-18</v>
+      </c>
+      <c r="G100" s="33">
+        <v>9.0241953402926103E-19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>372</v>
+      </c>
+      <c r="B101" t="s">
+        <v>314</v>
+      </c>
+      <c r="C101" s="42">
+        <v>-1.9773219577174801</v>
+      </c>
+      <c r="D101" s="42">
+        <v>0.226072006542309</v>
+      </c>
+      <c r="E101" s="33">
+        <v>2.2021759653187898E-18</v>
+      </c>
+      <c r="F101" s="33">
+        <v>5.2988729973158397E-17</v>
+      </c>
+      <c r="G101" s="33">
+        <v>5.0118487486565501E-18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>366</v>
+      </c>
+      <c r="B102" t="s">
+        <v>371</v>
+      </c>
+      <c r="C102" s="42">
+        <v>-2.0131374824288302</v>
+      </c>
+      <c r="D102" s="42">
+        <v>0.23593768015364699</v>
+      </c>
+      <c r="E102" s="33">
+        <v>1.4322261114614999E-17</v>
+      </c>
+      <c r="F102" s="33">
+        <v>7.9661745334834295E-17</v>
+      </c>
+      <c r="G102" s="33">
+        <v>3.1508974452153098E-17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>373</v>
+      </c>
+      <c r="B103" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="42">
+        <v>-2.7950667616921598</v>
+      </c>
+      <c r="D103" s="42">
+        <v>0.329000672194389</v>
+      </c>
+      <c r="E103" s="33">
+        <v>1.9686845758500601E-17</v>
+      </c>
+      <c r="F103" s="33">
+        <v>7.6258877249922599E-16</v>
+      </c>
+      <c r="G103" s="33">
+        <v>4.1913929679388502E-17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>373</v>
+      </c>
+      <c r="B104" t="s">
+        <v>374</v>
+      </c>
+      <c r="C104" s="42">
+        <v>-2.8898727236781099</v>
+      </c>
+      <c r="D104" s="42">
+        <v>0.37020462076013499</v>
+      </c>
+      <c r="E104" s="33">
+        <v>5.8961498313075103E-15</v>
+      </c>
+      <c r="F104" s="33">
+        <v>3.47321798006834E-13</v>
+      </c>
+      <c r="G104" s="33">
+        <v>1.2160809027071699E-14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>367</v>
+      </c>
+      <c r="B105" t="s">
+        <v>371</v>
+      </c>
+      <c r="C105" s="42">
+        <v>-1.81930377966416</v>
+      </c>
+      <c r="D105" s="42">
+        <v>0.23380415338132499</v>
+      </c>
+      <c r="E105" s="33">
+        <v>7.1774498243161995E-15</v>
+      </c>
+      <c r="F105" s="33">
+        <v>3.7221211308968602E-13</v>
+      </c>
+      <c r="G105" s="33">
+        <v>1.4354899648632399E-14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>372</v>
+      </c>
+      <c r="B106" t="s">
+        <v>373</v>
+      </c>
+      <c r="C106" s="42">
+        <v>2.52171711881003</v>
+      </c>
+      <c r="D106" s="42">
+        <v>0.32543405719025498</v>
+      </c>
+      <c r="E106" s="33">
+        <v>9.2779138779506098E-15</v>
+      </c>
+      <c r="F106" s="33">
+        <v>2.2596233472606801E-13</v>
+      </c>
+      <c r="G106" s="33">
+        <v>1.8010068116021699E-14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>365</v>
+      </c>
+      <c r="B107" t="s">
+        <v>370</v>
+      </c>
+      <c r="C107" s="42">
+        <v>1.75587140402425</v>
+      </c>
+      <c r="D107" s="42">
+        <v>0.23245349544395399</v>
+      </c>
+      <c r="E107" s="33">
+        <v>4.2323974031667597E-14</v>
+      </c>
+      <c r="F107" s="33">
+        <v>8.0898357475048195E-13</v>
+      </c>
+      <c r="G107" s="33">
+        <v>7.9810922459716001E-14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>314</v>
+      </c>
+      <c r="B108" t="s">
+        <v>370</v>
+      </c>
+      <c r="C108" s="42">
+        <v>1.7039723148353501</v>
+      </c>
+      <c r="D108" s="42">
+        <v>0.23162537182946299</v>
+      </c>
+      <c r="E108" s="33">
+        <v>1.88671228047308E-13</v>
+      </c>
+      <c r="F108" s="33">
+        <v>6.3320966766954296E-12</v>
+      </c>
+      <c r="G108" s="33">
+        <v>3.4589725142006499E-13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>372</v>
+      </c>
+      <c r="B109" t="s">
+        <v>368</v>
+      </c>
+      <c r="C109" s="42">
+        <v>-1.64677221124398</v>
+      </c>
+      <c r="D109" s="42">
+        <v>0.22629721969370001</v>
+      </c>
+      <c r="E109" s="33">
+        <v>3.4124319670641201E-13</v>
+      </c>
+      <c r="F109" s="33">
+        <v>1.9973445172247101E-12</v>
+      </c>
+      <c r="G109" s="33">
+        <v>6.0870408061143702E-13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>370</v>
+      </c>
+      <c r="B110" t="s">
+        <v>371</v>
+      </c>
+      <c r="C110" s="42">
+        <v>1.6045933080006001</v>
+      </c>
+      <c r="D110" s="42">
+        <v>0.23554022847467601</v>
+      </c>
+      <c r="E110" s="33">
+        <v>9.5986451676510707E-12</v>
+      </c>
+      <c r="F110" s="33">
+        <v>6.5275489215148404E-11</v>
+      </c>
+      <c r="G110" s="33">
+        <v>1.66713310806571E-11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>375</v>
+      </c>
+      <c r="B111" t="s">
+        <v>370</v>
+      </c>
+      <c r="C111" s="42">
+        <v>-2.23527585816064</v>
+      </c>
+      <c r="D111" s="42">
+        <v>0.336906224015115</v>
+      </c>
+      <c r="E111" s="33">
+        <v>3.2513614025820997E-11</v>
+      </c>
+      <c r="F111" s="33">
+        <v>5.7899717720318005E-10</v>
+      </c>
+      <c r="G111" s="33">
+        <v>5.5023039120620198E-11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>375</v>
+      </c>
+      <c r="B112" t="s">
+        <v>374</v>
+      </c>
+      <c r="C112" s="42">
+        <v>-2.3300818201465998</v>
+      </c>
+      <c r="D112" s="42">
+        <v>0.37952176772353002</v>
+      </c>
+      <c r="E112" s="33">
+        <v>8.27707407946588E-10</v>
+      </c>
+      <c r="F112" s="33">
+        <v>1.54077325388985E-8</v>
+      </c>
+      <c r="G112" s="33">
+        <v>1.3657172231118699E-9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>368</v>
+      </c>
+      <c r="B113" t="s">
+        <v>370</v>
+      </c>
+      <c r="C113" s="42">
+        <v>1.3734225683618499</v>
+      </c>
+      <c r="D113" s="42">
+        <v>0.23184006237935001</v>
+      </c>
+      <c r="E113" s="33">
+        <v>3.1418664316519E-9</v>
+      </c>
+      <c r="F113" s="33">
+        <v>1.7749859912889499E-8</v>
+      </c>
+      <c r="G113" s="33">
+        <v>5.05763864607379E-9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>372</v>
+      </c>
+      <c r="B114" t="s">
+        <v>375</v>
+      </c>
+      <c r="C114" s="42">
+        <v>1.96192621527851</v>
+      </c>
+      <c r="D114" s="42">
+        <v>0.33339005102442898</v>
+      </c>
+      <c r="E114" s="33">
+        <v>3.9859024748484001E-9</v>
+      </c>
+      <c r="F114" s="33">
+        <v>3.1133874036916898E-8</v>
+      </c>
+      <c r="G114" s="33">
+        <v>6.2635610319046397E-9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>374</v>
+      </c>
+      <c r="B115" t="s">
+        <v>371</v>
+      </c>
+      <c r="C115" s="42">
+        <v>1.6993992699865601</v>
+      </c>
+      <c r="D115" s="42">
+        <v>0.290025915605717</v>
+      </c>
+      <c r="E115" s="33">
+        <v>4.6433597889742899E-9</v>
+      </c>
+      <c r="F115" s="33">
+        <v>3.6820764442228298E-8</v>
+      </c>
+      <c r="G115" s="33">
+        <v>7.1270173505186799E-9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>365</v>
+      </c>
+      <c r="B116" t="s">
+        <v>374</v>
+      </c>
+      <c r="C116" s="42">
+        <v>1.66106544203829</v>
+      </c>
+      <c r="D116" s="42">
+        <v>0.28684933239681798</v>
+      </c>
+      <c r="E116" s="33">
+        <v>7.0083474288946601E-9</v>
+      </c>
+      <c r="F116" s="33">
+        <v>1.2253429637814901E-7</v>
+      </c>
+      <c r="G116" s="33">
+        <v>1.0512521143341901E-8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>372</v>
+      </c>
+      <c r="B117" t="s">
+        <v>371</v>
+      </c>
+      <c r="C117" s="42">
+        <v>1.33124366511847</v>
+      </c>
+      <c r="D117" s="42">
+        <v>0.23007936012094499</v>
+      </c>
+      <c r="E117" s="33">
+        <v>7.2073849398981204E-9</v>
+      </c>
+      <c r="F117" s="33">
+        <v>2.6096830363951301E-8</v>
+      </c>
+      <c r="G117" s="33">
+        <v>1.05708312451839E-8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>314</v>
+      </c>
+      <c r="B118" t="s">
+        <v>374</v>
+      </c>
+      <c r="C118" s="42">
+        <v>1.60916635284939</v>
+      </c>
+      <c r="D118" s="42">
+        <v>0.28612538483573102</v>
+      </c>
+      <c r="E118" s="33">
+        <v>1.8659626848441E-8</v>
+      </c>
+      <c r="F118" s="33">
+        <v>4.7303282017516102E-7</v>
+      </c>
+      <c r="G118" s="33">
+        <v>2.6772508086893698E-8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>369</v>
+      </c>
+      <c r="B119" t="s">
+        <v>371</v>
+      </c>
+      <c r="C119" s="42">
+        <v>-1.3814723631414001</v>
+      </c>
+      <c r="D119" s="42">
+        <v>0.24940961510187201</v>
+      </c>
+      <c r="E119" s="33">
+        <v>3.04255840483331E-8</v>
+      </c>
+      <c r="F119" s="33">
+        <v>9.7828416793304199E-8</v>
+      </c>
+      <c r="G119" s="33">
+        <v>4.2725288238084801E-8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>374</v>
+      </c>
+      <c r="B120" t="s">
+        <v>368</v>
+      </c>
+      <c r="C120" s="42">
+        <v>-1.2786166063758899</v>
+      </c>
+      <c r="D120" s="42">
+        <v>0.28628916293713802</v>
+      </c>
+      <c r="E120" s="33">
+        <v>7.9631644883807407E-6</v>
+      </c>
+      <c r="F120" s="33">
+        <v>4.0598585745207498E-5</v>
+      </c>
+      <c r="G120" s="33">
+        <v>1.0949351171523501E-5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>366</v>
+      </c>
+      <c r="B121" t="s">
+        <v>375</v>
+      </c>
+      <c r="C121" s="42">
+        <v>-1.38245493226879</v>
+      </c>
+      <c r="D121" s="42">
+        <v>0.33753467286206601</v>
+      </c>
+      <c r="E121" s="33">
+        <v>4.2081839905780199E-5</v>
+      </c>
+      <c r="F121" s="33">
+        <v>1.1621498079052599E-4</v>
+      </c>
+      <c r="G121" s="33">
+        <v>5.6681661913907997E-5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>373</v>
+      </c>
+      <c r="B122" t="s">
+        <v>371</v>
+      </c>
+      <c r="C122" s="42">
+        <v>-1.19047345369155</v>
+      </c>
+      <c r="D122" s="42">
+        <v>0.32745520861532101</v>
+      </c>
+      <c r="E122" s="33">
+        <v>2.7740898634877402E-4</v>
+      </c>
+      <c r="F122" s="33">
+        <v>5.7646784051697004E-4</v>
+      </c>
+      <c r="G122" s="33">
+        <v>3.6617986198038199E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>367</v>
+      </c>
+      <c r="B123" t="s">
+        <v>375</v>
+      </c>
+      <c r="C123" s="42">
+        <v>-1.1886212295041301</v>
+      </c>
+      <c r="D123" s="42">
+        <v>0.33579960726688102</v>
+      </c>
+      <c r="E123" s="33">
+        <v>4.0062116826331001E-4</v>
+      </c>
+      <c r="F123" s="33">
+        <v>9.1247453948316499E-4</v>
+      </c>
+      <c r="G123" s="33">
+        <v>5.1845092363487198E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>366</v>
+      </c>
+      <c r="B124" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" s="42">
+        <v>-0.63166511928742597</v>
+      </c>
+      <c r="D124" s="42">
+        <v>0.25148575761177999</v>
+      </c>
+      <c r="E124" s="44">
+        <v>1.2013988937908501E-2</v>
+      </c>
+      <c r="F124" s="44">
+        <v>2.9349932225702199E-2</v>
+      </c>
+      <c r="G124" s="44">
+        <v>1.5248524421191499E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>366</v>
+      </c>
+      <c r="B125" t="s">
+        <v>373</v>
+      </c>
+      <c r="C125" s="42">
+        <v>-0.82266402873727995</v>
+      </c>
+      <c r="D125" s="42">
+        <v>0.32922855898591002</v>
+      </c>
+      <c r="E125" s="44">
+        <v>1.24627748478424E-2</v>
+      </c>
+      <c r="F125" s="44">
+        <v>2.6544780432942099E-2</v>
+      </c>
+      <c r="G125" s="44">
+        <v>1.55196818859925E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>369</v>
+      </c>
+      <c r="B126" t="s">
+        <v>375</v>
+      </c>
+      <c r="C126" s="42">
+        <v>-0.75078981298137004</v>
+      </c>
+      <c r="D126" s="42">
+        <v>0.34598958636299298</v>
+      </c>
+      <c r="E126" s="44">
+        <v>3.0008507720380901E-2</v>
+      </c>
+      <c r="F126" s="44">
+        <v>5.2240393325001598E-2</v>
+      </c>
+      <c r="G126" s="44">
+        <v>3.6677064991576698E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>367</v>
+      </c>
+      <c r="B127" t="s">
+        <v>373</v>
+      </c>
+      <c r="C127" s="42">
+        <v>-0.62883032597261301</v>
+      </c>
+      <c r="D127" s="42">
+        <v>0.32786228628622999</v>
+      </c>
+      <c r="E127" s="44">
+        <v>5.5114700452506799E-2</v>
+      </c>
+      <c r="F127" s="44">
+        <v>8.1163897320025602E-2</v>
+      </c>
+      <c r="G127" s="44">
+        <v>6.6137640543008205E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>375</v>
+      </c>
+      <c r="B128" t="s">
+        <v>371</v>
+      </c>
+      <c r="C128" s="42">
+        <v>-0.63068255016003605</v>
+      </c>
+      <c r="D128" s="42">
+        <v>0.33575723513445199</v>
+      </c>
+      <c r="E128" s="44">
+        <v>6.0328029063784198E-2</v>
+      </c>
+      <c r="F128" s="44">
+        <v>8.5521645731388402E-2</v>
+      </c>
+      <c r="G128" s="44">
+        <v>7.1100891396602806E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>367</v>
+      </c>
+      <c r="B129" t="s">
+        <v>369</v>
+      </c>
+      <c r="C129" s="42">
+        <v>-0.43783141652275898</v>
+      </c>
+      <c r="D129" s="42">
+        <v>0.24950215019965999</v>
+      </c>
+      <c r="E129" s="44">
+        <v>7.9290064925043702E-2</v>
+      </c>
+      <c r="F129" s="44">
+        <v>0.11808529706451</v>
+      </c>
+      <c r="G129" s="44">
+        <v>9.1809548860576906E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>365</v>
+      </c>
+      <c r="B130" t="s">
+        <v>368</v>
+      </c>
+      <c r="C130" s="42">
+        <v>0.38244883566240001</v>
+      </c>
+      <c r="D130" s="42">
+        <v>0.226608986335402</v>
+      </c>
+      <c r="E130" s="44">
+        <v>9.1468111895682699E-2</v>
+      </c>
+      <c r="F130" s="44">
+        <v>0.13381314058914501</v>
+      </c>
+      <c r="G130" s="44">
+        <v>0.104084403191639</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>314</v>
+      </c>
+      <c r="B131" t="s">
+        <v>368</v>
+      </c>
+      <c r="C131" s="42">
+        <v>0.330549746473497</v>
+      </c>
+      <c r="D131" s="42">
+        <v>0.225743483680373</v>
+      </c>
+      <c r="E131" s="44">
+        <v>0.143119784613605</v>
+      </c>
+      <c r="F131" s="44">
+        <v>0.20531792119466699</v>
+      </c>
+      <c r="G131" s="44">
+        <v>0.16010009804233799</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>373</v>
+      </c>
+      <c r="B132" t="s">
+        <v>375</v>
+      </c>
+      <c r="C132" s="42">
+        <v>-0.55979090353151695</v>
+      </c>
+      <c r="D132" s="42">
+        <v>0.40622257280590501</v>
+      </c>
+      <c r="E132" s="44">
+        <v>0.16819097713650399</v>
+      </c>
+      <c r="F132" s="44">
+        <v>0.338573640077456</v>
+      </c>
+      <c r="G132" s="44">
+        <v>0.185010074850154</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>372</v>
+      </c>
+      <c r="B133" t="s">
+        <v>374</v>
+      </c>
+      <c r="C133" s="42">
+        <v>-0.36815560486808602</v>
+      </c>
+      <c r="D133" s="42">
+        <v>0.28660489105140202</v>
+      </c>
+      <c r="E133" s="44">
+        <v>0.19895288418524801</v>
+      </c>
+      <c r="F133" s="44">
+        <v>0.31139133155897603</v>
+      </c>
+      <c r="G133" s="44">
+        <v>0.21526049764305599</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>372</v>
+      </c>
+      <c r="B134" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="42">
+        <v>-0.27334964288212699</v>
+      </c>
+      <c r="D134" s="42">
+        <v>0.23215649736413799</v>
+      </c>
+      <c r="E134" s="44">
+        <v>0.23902114102622901</v>
+      </c>
+      <c r="F134" s="44">
+        <v>0.34546139170328299</v>
+      </c>
+      <c r="G134" s="44">
+        <v>0.25444185980211498</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>367</v>
+      </c>
+      <c r="B135" t="s">
+        <v>366</v>
+      </c>
+      <c r="C135" s="42">
+        <v>0.19383370276466699</v>
+      </c>
+      <c r="D135" s="42">
+        <v>0.23612590256614399</v>
+      </c>
+      <c r="E135" s="44">
+        <v>0.41170817826971601</v>
+      </c>
+      <c r="F135" s="44">
+        <v>0.49776045750827602</v>
+      </c>
+      <c r="G135" s="44">
+        <v>0.43131332961589303</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>373</v>
+      </c>
+      <c r="B136" t="s">
+        <v>369</v>
+      </c>
+      <c r="C136" s="42">
+        <v>0.19099890944985301</v>
+      </c>
+      <c r="D136" s="42">
+        <v>0.33814919087242701</v>
+      </c>
+      <c r="E136" s="44">
+        <v>0.57218517119360601</v>
+      </c>
+      <c r="F136" s="44">
+        <v>0.69052464983695905</v>
+      </c>
+      <c r="G136" s="44">
+        <v>0.59006595779340598</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>374</v>
+      </c>
+      <c r="B137" t="s">
+        <v>370</v>
+      </c>
+      <c r="C137" s="42">
+        <v>9.4805961985958795E-2</v>
+      </c>
+      <c r="D137" s="42">
+        <v>0.29106834819947203</v>
+      </c>
+      <c r="E137" s="44">
+        <v>0.74463834362256298</v>
+      </c>
+      <c r="F137" s="44">
+        <v>0.88447947694889795</v>
+      </c>
+      <c r="G137" s="44">
+        <v>0.75609431813983297</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>365</v>
+      </c>
+      <c r="B138" t="s">
+        <v>314</v>
+      </c>
+      <c r="C138" s="42">
+        <v>5.1899089188903402E-2</v>
+      </c>
+      <c r="D138" s="42">
+        <v>0.226384707270015</v>
+      </c>
+      <c r="E138" s="44">
+        <v>0.81867325658967305</v>
+      </c>
+      <c r="F138" s="44">
+        <v>0.87148609785134201</v>
+      </c>
+      <c r="G138" s="44">
+        <v>0.81867325658967305</v>
       </c>
     </row>
   </sheetData>
